--- a/prds-desktop/src/frontend/assets/templates-excel/list-of-medicine.xlsx
+++ b/prds-desktop/src/frontend/assets/templates-excel/list-of-medicine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\prds\prds-desktop\src\frontend\assets\templates-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0BBF0BB-8F97-4F30-8616-3E9A4FF4F8A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB1B6AFA-382C-4A30-B02A-1B67FC2924C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{0DD93CDD-0E2E-444C-B7CF-82A809FF3AF9}"/>
   </bookViews>
@@ -39,12 +39,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Generic Name</t>
-  </si>
-  <si>
-    <t>Brand Name</t>
   </si>
   <si>
     <t>Dosage</t>
@@ -54,9 +51,6 @@
   </si>
   <si>
     <t>Category</t>
-  </si>
-  <si>
-    <t>Unit Cost</t>
   </si>
   <si>
     <r>
@@ -117,10 +111,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -455,50 +449,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86CC83FB-3750-417C-ADAC-B83CEFDC8E52}">
-  <dimension ref="D1:I2"/>
+  <dimension ref="D1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="58.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" customWidth="1"/>
-    <col min="6" max="6" width="47" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="38.7109375" customWidth="1"/>
-    <col min="9" max="9" width="9.42578125" customWidth="1"/>
+    <col min="5" max="5" width="47" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="7" max="7" width="38.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D1" s="1" t="s">
-        <v>6</v>
+    <row r="1" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D1" s="2" t="s">
+        <v>4</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D2" s="2" t="s">
+    <row r="2" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
